--- a/Output/Cluster_Visualizations/cluster_size_summary.xlsx
+++ b/Output/Cluster_Visualizations/cluster_size_summary.xlsx
@@ -18,10 +18,10 @@
     <t>cluster_ch</t>
   </si>
   <si>
-    <t>Cluster 1</t>
+    <t>Cluster 2</t>
   </si>
   <si>
-    <t>Cluster 2</t>
+    <t>Cluster 1</t>
   </si>
   <si>
     <t>cluster_dh</t>
@@ -30,10 +30,10 @@
     <t>cluster_elbow</t>
   </si>
   <si>
-    <t>Cluster 4</t>
+    <t>Cluster 3</t>
   </si>
   <si>
-    <t>Cluster 3</t>
+    <t>Cluster 4</t>
   </si>
   <si>
     <t>cluster_gap</t>
@@ -140,19 +140,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G2" s="1">
         <v>271</v>
@@ -169,19 +169,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G3" s="1">
-        <v>363</v>
+        <v>203</v>
       </c>
       <c r="H3" s="1">
         <v>108</v>
@@ -189,19 +189,19 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1">
         <v>659</v>
@@ -215,25 +215,25 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1">
         <v>659</v>
       </c>
       <c r="G5" s="1">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="H5" s="1">
         <v>108</v>
@@ -241,16 +241,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
         <v>2</v>
@@ -273,19 +273,19 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G7" s="1">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="H7" s="1">
         <v>108</v>
@@ -293,16 +293,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
         <v>1</v>
@@ -325,19 +325,19 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G9" s="1">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="H9" s="1">
         <v>108</v>
@@ -345,16 +345,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
         <v>1</v>
@@ -377,19 +377,19 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="s">
         <v>2</v>
       </c>
       <c r="F11" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G11" s="1">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="H11" s="1">
         <v>108</v>
@@ -397,25 +397,25 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="1">
         <v>659</v>
       </c>
       <c r="G12" s="1">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="H12" s="1">
         <v>108</v>
@@ -423,19 +423,19 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1">
         <v>659</v>
@@ -452,19 +452,19 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G14" s="1">
         <v>288</v>
@@ -478,22 +478,22 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G15" s="1">
-        <v>363</v>
+        <v>271</v>
       </c>
       <c r="H15" s="1">
         <v>108</v>
@@ -507,19 +507,19 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G16" s="1">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="H16" s="1">
         <v>108</v>
@@ -527,19 +527,19 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="1">
         <v>466</v>
@@ -556,22 +556,22 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
         <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G18" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H18" s="1">
         <v>154</v>
@@ -585,19 +585,19 @@
         <v>2</v>
       </c>
       <c r="C19" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G19" s="1">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="H19" s="1">
         <v>154</v>
@@ -605,19 +605,19 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1">
         <v>659</v>
@@ -634,19 +634,19 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="s">
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G21" s="1">
         <v>363</v>
@@ -657,25 +657,25 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="1">
         <v>466</v>
       </c>
       <c r="G22" s="1">
-        <v>363</v>
+        <v>203</v>
       </c>
       <c r="H22" s="1">
         <v>154</v>
@@ -692,16 +692,16 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G23" s="1">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="H23" s="1">
         <v>154</v>
@@ -715,16 +715,16 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" t="s">
         <v>2</v>
       </c>
       <c r="F24" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G24" s="1">
         <v>363</v>
@@ -735,16 +735,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="s">
         <v>2</v>
@@ -753,7 +753,7 @@
         <v>659</v>
       </c>
       <c r="G25" s="1">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="H25" s="1">
         <v>154</v>
@@ -764,22 +764,22 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G26" s="1">
-        <v>203</v>
+        <v>363</v>
       </c>
       <c r="H26" s="1">
         <v>154</v>
@@ -787,25 +787,25 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F27" s="1">
         <v>466</v>
       </c>
       <c r="G27" s="1">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="H27" s="1">
         <v>154</v>
@@ -813,25 +813,25 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="1">
         <v>659</v>
       </c>
       <c r="G28" s="1">
-        <v>363</v>
+        <v>203</v>
       </c>
       <c r="H28" s="1">
         <v>154</v>
@@ -839,16 +839,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>2</v>
@@ -857,7 +857,7 @@
         <v>659</v>
       </c>
       <c r="G29" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H29" s="1">
         <v>210</v>
@@ -865,25 +865,25 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="1">
         <v>659</v>
       </c>
       <c r="G30" s="1">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="H30" s="1">
         <v>210</v>
@@ -891,16 +891,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" t="s">
         <v>2</v>
@@ -926,16 +926,16 @@
         <v>2</v>
       </c>
       <c r="D32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G32" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H32" s="1">
         <v>210</v>
@@ -952,16 +952,16 @@
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
         <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G33" s="1">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="H33" s="1">
         <v>210</v>
@@ -969,25 +969,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" s="1">
         <v>466</v>
       </c>
       <c r="G34" s="1">
-        <v>363</v>
+        <v>203</v>
       </c>
       <c r="H34" s="1">
         <v>210</v>
@@ -995,25 +995,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" s="1">
         <v>466</v>
       </c>
       <c r="G35" s="1">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="H35" s="1">
         <v>210</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="s">
         <v>2</v>
@@ -1039,7 +1039,7 @@
         <v>466</v>
       </c>
       <c r="G36" s="1">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="H36" s="1">
         <v>210</v>
@@ -1047,16 +1047,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" t="s">
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
         <v>1</v>
@@ -1065,7 +1065,7 @@
         <v>466</v>
       </c>
       <c r="G37" s="1">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="H37" s="1">
         <v>210</v>
@@ -1076,22 +1076,22 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="s">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G38" s="1">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="H38" s="1">
         <v>210</v>
@@ -1099,16 +1099,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" t="s">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>659</v>
       </c>
       <c r="G39" s="1">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="H39" s="1">
         <v>210</v>
@@ -1125,25 +1125,25 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="s">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="1">
         <v>659</v>
       </c>
       <c r="G40" s="1">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="H40" s="1">
         <v>210</v>
@@ -1151,16 +1151,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>1</v>
@@ -1169,7 +1169,7 @@
         <v>659</v>
       </c>
       <c r="G41" s="1">
-        <v>363</v>
+        <v>271</v>
       </c>
       <c r="H41" s="1">
         <v>210</v>
@@ -1180,22 +1180,22 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G42" s="1">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="H42" s="1">
         <v>210</v>
@@ -1203,25 +1203,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="s">
         <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="1">
         <v>659</v>
       </c>
       <c r="G43" s="1">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="H43" s="1">
         <v>210</v>
@@ -1229,16 +1229,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
         <v>2</v>
@@ -1255,19 +1255,19 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="1">
         <v>466</v>
@@ -1281,19 +1281,19 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" s="1">
         <v>466</v>
@@ -1307,16 +1307,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
         <v>2</v>
@@ -1339,16 +1339,16 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G48" s="1">
         <v>271</v>
@@ -1359,25 +1359,25 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D49" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="1">
         <v>466</v>
       </c>
       <c r="G49" s="1">
-        <v>363</v>
+        <v>271</v>
       </c>
       <c r="H49" s="1">
         <v>109</v>
@@ -1385,16 +1385,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E50" t="s">
         <v>1</v>
@@ -1411,19 +1411,19 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="1">
         <v>466</v>
@@ -1443,19 +1443,19 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G52" s="1">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="H52" s="1">
         <v>109</v>
@@ -1463,19 +1463,19 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="s">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="1">
         <v>659</v>
@@ -1489,25 +1489,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D54" t="s">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="1">
         <v>659</v>
       </c>
       <c r="G54" s="1">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="H54" s="1">
         <v>106</v>
@@ -1521,7 +1521,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
         <v>8</v>
@@ -1530,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G55" s="1">
         <v>271</v>
@@ -1556,10 +1556,10 @@
         <v>2</v>
       </c>
       <c r="F56" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G56" s="1">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="H56" s="1">
         <v>106</v>
@@ -1570,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="s">
         <v>2</v>
@@ -1579,13 +1579,13 @@
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G57" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H57" s="1">
         <v>106</v>
@@ -1593,25 +1593,25 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D58" t="s">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" s="1">
         <v>466</v>
       </c>
       <c r="G58" s="1">
-        <v>203</v>
+        <v>363</v>
       </c>
       <c r="H58" s="1">
         <v>106</v>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
@@ -1631,13 +1631,13 @@
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G59" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H59" s="1">
         <v>106</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1657,13 +1657,13 @@
         <v>8</v>
       </c>
       <c r="E60" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F60" s="1">
         <v>659</v>
       </c>
       <c r="G60" s="1">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="H60" s="1">
         <v>106</v>
@@ -1671,25 +1671,25 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B61" t="s">
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D61" t="s">
         <v>8</v>
       </c>
       <c r="E61" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F61" s="1">
         <v>659</v>
       </c>
       <c r="G61" s="1">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="H61" s="1">
         <v>106</v>
@@ -1697,25 +1697,25 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B62" t="s">
         <v>1</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D62" t="s">
         <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" s="1">
         <v>659</v>
       </c>
       <c r="G62" s="1">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="H62" s="1">
         <v>106</v>
@@ -1729,16 +1729,16 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G63" s="1">
         <v>288</v>
@@ -1755,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
@@ -1764,10 +1764,10 @@
         <v>1</v>
       </c>
       <c r="F64" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G64" s="1">
-        <v>271</v>
+        <v>363</v>
       </c>
       <c r="H64" s="1">
         <v>170</v>
@@ -1781,7 +1781,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" t="s">
         <v>9</v>
@@ -1790,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G65" s="1">
         <v>288</v>
@@ -1807,19 +1807,19 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D66" t="s">
         <v>9</v>
       </c>
       <c r="E66" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G66" s="1">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="H66" s="1">
         <v>170</v>
@@ -1833,7 +1833,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D67" t="s">
         <v>9</v>
@@ -1842,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="F67" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G67" s="1">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="H67" s="1">
         <v>170</v>
@@ -1856,19 +1856,19 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
       </c>
       <c r="E68" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G68" s="1">
         <v>271</v>
@@ -1882,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="E69" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G69" s="1">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="H69" s="1">
         <v>170</v>
@@ -1911,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
@@ -1920,10 +1920,10 @@
         <v>2</v>
       </c>
       <c r="F70" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G70" s="1">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="H70" s="1">
         <v>170</v>
@@ -1937,16 +1937,16 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G71" s="1">
         <v>288</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D72" t="s">
         <v>9</v>
@@ -1972,7 +1972,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G72" s="1">
         <v>288</v>
@@ -1983,13 +1983,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D73" t="s">
         <v>9</v>
@@ -2009,19 +2009,19 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B74" t="s">
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74" t="s">
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="1">
         <v>659</v>
@@ -2041,7 +2041,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D75" t="s">
         <v>10</v>
@@ -2050,10 +2050,10 @@
         <v>1</v>
       </c>
       <c r="F75" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G75" s="1">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="H75" s="1">
         <v>122</v>
@@ -2061,25 +2061,25 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D76" t="s">
         <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="1">
         <v>659</v>
       </c>
       <c r="G76" s="1">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="H76" s="1">
         <v>122</v>
@@ -2087,7 +2087,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B77" t="s">
         <v>2</v>
@@ -2105,7 +2105,7 @@
         <v>466</v>
       </c>
       <c r="G77" s="1">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="H77" s="1">
         <v>122</v>
@@ -2113,13 +2113,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
         <v>1</v>
       </c>
       <c r="C78" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78" t="s">
         <v>10</v>
@@ -2139,25 +2139,25 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D79" t="s">
         <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" s="1">
         <v>659</v>
       </c>
       <c r="G79" s="1">
-        <v>288</v>
+        <v>203</v>
       </c>
       <c r="H79" s="1">
         <v>122</v>
@@ -2165,13 +2165,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D80" t="s">
         <v>10</v>
@@ -2183,7 +2183,7 @@
         <v>659</v>
       </c>
       <c r="G80" s="1">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="H80" s="1">
         <v>122</v>
@@ -2191,13 +2191,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B81" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D81" t="s">
         <v>10</v>
@@ -2220,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -2232,10 +2232,10 @@
         <v>1</v>
       </c>
       <c r="F82" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G82" s="1">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="H82" s="1">
         <v>122</v>
@@ -2258,10 +2258,10 @@
         <v>2</v>
       </c>
       <c r="F83" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G83" s="1">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="H83" s="1">
         <v>146</v>
@@ -2272,7 +2272,7 @@
         <v>2</v>
       </c>
       <c r="B84" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="s">
         <v>6</v>
@@ -2284,10 +2284,10 @@
         <v>1</v>
       </c>
       <c r="F84" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G84" s="1">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="H84" s="1">
         <v>146</v>
@@ -2295,25 +2295,25 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="1">
         <v>659</v>
       </c>
       <c r="G85" s="1">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="H85" s="1">
         <v>146</v>
@@ -2321,10 +2321,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="s">
         <v>2</v>
@@ -2333,13 +2333,13 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" s="1">
         <v>659</v>
       </c>
       <c r="G86" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H86" s="1">
         <v>146</v>
@@ -2347,19 +2347,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" s="1">
         <v>659</v>
@@ -2373,19 +2373,19 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" s="1">
         <v>466</v>
@@ -2414,10 +2414,10 @@
         <v>1</v>
       </c>
       <c r="F89" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G89" s="1">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="H89" s="1">
         <v>146</v>
@@ -2428,7 +2428,7 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="s">
         <v>2</v>
@@ -2440,10 +2440,10 @@
         <v>2</v>
       </c>
       <c r="F90" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G90" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H90" s="1">
         <v>146</v>
@@ -2451,10 +2451,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -2469,7 +2469,7 @@
         <v>659</v>
       </c>
       <c r="G91" s="1">
-        <v>363</v>
+        <v>288</v>
       </c>
       <c r="H91" s="1">
         <v>146</v>
@@ -2483,16 +2483,16 @@
         <v>1</v>
       </c>
       <c r="C92" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="1">
-        <v>659</v>
+        <v>466</v>
       </c>
       <c r="G92" s="1">
         <v>271</v>
@@ -2503,10 +2503,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="s">
         <v>1</v>
@@ -2521,7 +2521,7 @@
         <v>659</v>
       </c>
       <c r="G93" s="1">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="H93" s="1">
         <v>146</v>
@@ -2529,19 +2529,19 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" s="1">
         <v>466</v>
@@ -2555,19 +2555,19 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="1">
         <v>466</v>
@@ -2581,13 +2581,13 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
@@ -2622,10 +2622,10 @@
         <v>1</v>
       </c>
       <c r="F97" s="1">
-        <v>466</v>
+        <v>659</v>
       </c>
       <c r="G97" s="1">
-        <v>271</v>
+        <v>203</v>
       </c>
       <c r="H97" s="1">
         <v>146</v>
@@ -2633,19 +2633,19 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" s="1">
         <v>659</v>
@@ -2659,25 +2659,25 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
       </c>
       <c r="E99" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="1">
         <v>659</v>
       </c>
       <c r="G99" s="1">
-        <v>203</v>
+        <v>363</v>
       </c>
       <c r="H99" s="1">
         <v>146</v>
